--- a/diseases/d164/2020-2025.xlsx
+++ b/diseases/d164/2020-2025.xlsx
@@ -26177,12 +26177,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -26207,7 +26207,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -26216,84 +26216,93 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P174" t="n">
+        <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26320,17 +26329,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -26355,7 +26364,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -26364,84 +26373,168 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O175" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P175" t="n">
+        <v>1</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Hantavirus infection, non-hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Hantavirus infection, non-hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26473,12 +26566,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -26503,68 +26596,74 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P176" t="n">
+        <v>1</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -26574,17 +26673,17 @@
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
@@ -26616,17 +26715,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -26651,68 +26750,152 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P177" t="n">
+        <v>1</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Hantavirus infection, non-hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Hantavirus infection, non-hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:US-AZ:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -26722,17 +26905,17 @@
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
@@ -26799,12 +26982,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -26947,12 +27130,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N179" t="n">
@@ -27095,12 +27278,12 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N180" t="n">
@@ -27243,12 +27426,12 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N181" t="n">
@@ -27391,12 +27574,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N182" t="n">
@@ -27509,12 +27692,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -27539,93 +27722,102 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P183" t="n">
+        <v>1</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>0.0002911400252945365</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27652,17 +27844,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -27687,93 +27879,177 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27805,12 +28081,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -27835,68 +28111,74 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>1</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -27906,17 +28188,17 @@
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
@@ -27948,17 +28230,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -27983,68 +28265,152 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-05-20</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P186" t="n">
+        <v>1</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:US-AZ:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -28054,17 +28420,17 @@
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
@@ -28131,12 +28497,12 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N187" t="n">
@@ -28279,12 +28645,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N188" t="n">
@@ -28427,12 +28793,12 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N189" t="n">
@@ -28575,12 +28941,12 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N190" t="n">
@@ -28723,12 +29089,12 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N191" t="n">
@@ -28871,12 +29237,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -29019,12 +29385,12 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N193" t="n">
@@ -29167,12 +29533,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -29315,12 +29681,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N195" t="n">
@@ -29463,12 +29829,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -29611,12 +29977,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -29759,12 +30125,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -29907,12 +30273,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N199" t="n">
@@ -30055,12 +30421,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N200" t="n">
@@ -30203,12 +30569,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -30351,12 +30717,12 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N202" t="n">
@@ -30499,12 +30865,12 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N203" t="n">
@@ -30647,12 +31013,12 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N204" t="n">
@@ -30795,12 +31161,12 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -30943,12 +31309,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N206" t="n">
@@ -31091,12 +31457,12 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N207" t="n">
@@ -31239,12 +31605,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -31387,12 +31753,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -31535,12 +31901,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -31683,12 +32049,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -31831,12 +32197,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -31979,12 +32345,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -32127,12 +32493,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -32275,12 +32641,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -32423,12 +32789,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N216" t="n">
@@ -32571,12 +32937,12 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N217" t="n">
@@ -32719,12 +33085,12 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -32867,12 +33233,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -33015,12 +33381,12 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -33163,12 +33529,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -33311,12 +33677,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -33459,12 +33825,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -33607,12 +33973,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -33755,12 +34121,12 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -33903,12 +34269,12 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -34051,12 +34417,12 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -34199,12 +34565,12 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N228" t="n">
@@ -34347,12 +34713,12 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N229" t="n">
@@ -34495,12 +34861,12 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N230" t="n">
@@ -34643,12 +35009,12 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -34791,12 +35157,12 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N232" t="n">
@@ -34939,12 +35305,12 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N233" t="n">
@@ -35087,12 +35453,12 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -35235,12 +35601,12 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N235" t="n">
@@ -35383,12 +35749,12 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N236" t="n">
@@ -35531,12 +35897,12 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -35679,12 +36045,12 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N238" t="n">
@@ -35827,12 +36193,12 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N239" t="n">
@@ -35975,12 +36341,12 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N240" t="n">
@@ -36123,12 +36489,12 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -36271,12 +36637,12 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N242" t="n">
@@ -36419,12 +36785,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -36567,12 +36933,12 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N244" t="n">
@@ -36685,12 +37051,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -36715,93 +37081,102 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P245" t="n">
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>0.0002894971273069784</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36828,17 +37203,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -36863,93 +37238,177 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P246" t="n">
+        <v>1</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36981,12 +37440,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -37011,68 +37470,74 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P247" t="n">
+        <v>1</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -37082,17 +37547,17 @@
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
@@ -37124,17 +37589,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -37159,68 +37624,152 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P248" t="n">
+        <v>1</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:US-AZ:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -37230,17 +37779,17 @@
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
@@ -37307,12 +37856,12 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N249" t="n">
@@ -37455,12 +38004,12 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N250" t="n">
@@ -37603,12 +38152,12 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N251" t="n">
@@ -37751,12 +38300,12 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N252" t="n">
@@ -37899,12 +38448,12 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N253" t="n">
@@ -38047,12 +38596,12 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N254" t="n">
@@ -38195,12 +38744,12 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -38343,12 +38892,12 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -38491,12 +39040,12 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N257" t="n">
@@ -38639,12 +39188,12 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N258" t="n">
@@ -38787,12 +39336,12 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N259" t="n">
@@ -38935,12 +39484,12 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -39083,12 +39632,12 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N261" t="n">
@@ -39231,12 +39780,12 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N262" t="n">
@@ -39379,12 +39928,12 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N263" t="n">
@@ -39527,12 +40076,12 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -39675,12 +40224,12 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -39823,12 +40372,12 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N266" t="n">
@@ -39971,12 +40520,12 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N267" t="n">
@@ -40119,12 +40668,12 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N268" t="n">
@@ -40267,12 +40816,12 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N269" t="n">
@@ -40415,12 +40964,12 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N270" t="n">
@@ -40563,12 +41112,12 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N271" t="n">
@@ -40711,12 +41260,12 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N272" t="n">
@@ -40859,12 +41408,12 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N273" t="n">
@@ -41007,12 +41556,12 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N274" t="n">
@@ -41155,12 +41704,12 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -41303,12 +41852,12 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N276" t="n">
@@ -41451,12 +42000,12 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N277" t="n">
@@ -41599,12 +42148,12 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -41747,12 +42296,12 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -41895,12 +42444,12 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -42043,12 +42592,12 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -42191,12 +42740,12 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N282" t="n">
@@ -42339,12 +42888,12 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N283" t="n">
@@ -42487,12 +43036,12 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N284" t="n">
@@ -42605,12 +43154,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -42635,93 +43184,102 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P285" t="n">
+        <v>1</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>0.0002879555610852622</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR285" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42748,17 +43306,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -42783,93 +43341,177 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
-      <c r="R286" t="n">
-        <v>0</v>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P286" t="n">
+        <v>1</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
+        <v>1</v>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR286" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS286" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42901,12 +43543,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -42931,68 +43573,74 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P287" t="n">
+        <v>1</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -43002,17 +43650,17 @@
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
@@ -43044,17 +43692,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-AZ</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Arizona, United States</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -43079,68 +43727,152 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
-      <c r="R288" t="n">
-        <v>0</v>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P288" t="n">
+        <v>1</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:US-AZ:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
       </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR288" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS288" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -43150,17 +43882,17 @@
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
@@ -43227,12 +43959,12 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N289" t="n">
@@ -43375,12 +44107,12 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N290" t="n">
@@ -43523,12 +44255,12 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N291" t="n">
@@ -43671,12 +44403,12 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N292" t="n">
@@ -43819,12 +44551,12 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N293" t="n">
@@ -43967,12 +44699,12 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N294" t="n">
@@ -44115,12 +44847,12 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N295" t="n">
@@ -44263,12 +44995,12 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N296" t="n">
@@ -44381,12 +45113,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -44411,93 +45143,102 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q297" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P297" t="n">
+        <v>1</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>0.0002879555610852622</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR297" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS297" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ297" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44524,17 +45265,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -44559,93 +45300,177 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
-      <c r="R298" t="n">
-        <v>0</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P298" t="n">
+        <v>1</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN298" t="b">
+        <v>1</v>
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR298" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44677,12 +45502,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-ID</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Idaho, United States</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -44707,68 +45532,79 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
-      <c r="R299" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P299" t="n">
+        <v>1</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR299" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS299" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ299" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -44778,17 +45614,17 @@
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
@@ -44820,17 +45656,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-ID</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Idaho, United States</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -44855,68 +45691,152 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
-      <c r="R300" t="n">
-        <v>0</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P300" t="n">
+        <v>1</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>country:US-ID:national</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN300" t="b">
+        <v>1</v>
       </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR300" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -44926,17 +45846,17 @@
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
@@ -45003,12 +45923,12 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N301" t="n">
@@ -45151,12 +46071,12 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N302" t="n">
@@ -45299,12 +46219,12 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N303" t="n">
@@ -45447,12 +46367,12 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N304" t="n">
@@ -45595,12 +46515,12 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N305" t="n">
@@ -45743,12 +46663,12 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N306" t="n">
@@ -45891,12 +46811,12 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N307" t="n">
@@ -46039,12 +46959,12 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N308" t="n">
@@ -46187,12 +47107,12 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N309" t="n">
@@ -46335,12 +47255,12 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N310" t="n">
@@ -46483,12 +47403,12 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N311" t="n">
@@ -46631,12 +47551,12 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N312" t="n">
@@ -46779,12 +47699,12 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="N313" t="n">
@@ -46927,12 +47847,12 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="N314" t="n">
@@ -47012,6 +47932,2966 @@
         </is>
       </c>
       <c r="BC314" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>0</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr"/>
+      <c r="AT315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>0</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
+      <c r="AT316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>0</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr"/>
+      <c r="AT317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>0</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr"/>
+      <c r="AT318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>0</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr"/>
+      <c r="AT319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>0</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr"/>
+      <c r="AT320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr"/>
+      <c r="AT321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
+      <c r="AT322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>0</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>0</v>
+      </c>
+      <c r="R324" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr"/>
+      <c r="AT324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>0</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR326" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr"/>
+      <c r="AT326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>0</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr"/>
+      <c r="AT327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>0</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR328" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr"/>
+      <c r="AT328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr"/>
+      <c r="AT329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>0</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR330" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr"/>
+      <c r="AT330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA330" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>0</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR331" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr"/>
+      <c r="AT331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>0</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR332" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr"/>
+      <c r="AT332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA332" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>0</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr"/>
+      <c r="AT333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA333" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB333" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC333" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr"/>
+      <c r="AT334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -47133,7 +51013,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -47143,7 +51023,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
@@ -47163,7 +51043,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -47173,7 +51053,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -47195,7 +51075,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
